--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-14.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-14.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -76,6 +80,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -541,29 +546,29 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宝联社区</t>
+          <t>营盘路社区</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.9</v>
+        <v>15.2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.7</v>
+        <v>56.1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>135.1</v>
+        <v>162.1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -578,29 +583,29 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>营盘路社区</t>
+          <t>宝联社区</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15.2</v>
+        <v>30.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>56.1</v>
+        <v>27.7</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>162.1</v>
+        <v>135.1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -615,29 +620,29 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>胜利四路社区</t>
+          <t>汕头路社区</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13.6</v>
+        <v>35.9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45.5</v>
+        <v>25.6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>22.7</v>
+        <v>7.7</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>215.9</v>
+        <v>248.7</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -652,29 +657,29 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>汕头路社区</t>
+          <t>胜利四路社区</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35.9</v>
+        <v>13.6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25.6</v>
+        <v>45.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7.7</v>
+        <v>22.7</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>248.7</v>
+        <v>215.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -726,33 +731,33 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>朝阳路社区</t>
+          <t>深圳路社区</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.8</v>
+        <v>22.8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>638.1</v>
+        <v>5.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>594</v>
+        <v>7</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -763,33 +768,33 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>万达社区</t>
+          <t>西峡社区</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>105.1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>72.5</v>
+        <v>5.1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>653.6</v>
+        <v>39.7</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>501</v>
+        <v>35</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -800,33 +805,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>港务社区</t>
+          <t>金安岭社区</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.9</v>
+        <v>130.4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>78.3</v>
+        <v>16.1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>14.2</v>
+        <v>19.6</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>315.1</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -837,33 +842,33 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>建设社区</t>
+          <t>镇境山社区</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>78.8</v>
+        <v>5.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>13.6</v>
+        <v>19.2</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>484.8</v>
+        <v>1.3</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>372</v>
+        <v>5</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -874,33 +879,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>伍临路社区</t>
+          <t>幸福路社区</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>363.6</v>
-      </c>
       <c r="H12" s="2" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>221</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -911,33 +916,33 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>大学路社区</t>
+          <t>新隆康路社区</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>36.2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45.4</v>
+        <v>6.9</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>183.5</v>
+        <v>42.3</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>222</v>
+        <v>64</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -948,33 +953,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>岳湾路社区</t>
+          <t>果园路社区</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22.9</v>
+        <v>11.8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2.4</v>
+        <v>28</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>248.2</v>
+        <v>66.7</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>225</v>
+        <v>73</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -985,33 +990,33 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>张家湾社区</t>
+          <t>桥北社区</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>71.8</v>
-      </c>
       <c r="F15" s="2" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>407.7</v>
-      </c>
       <c r="H15" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>187</v>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>客观隐患高·诉求未暴露</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1022,33 +1027,33 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>体育场路社区</t>
+          <t>朝阳路社区</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32.6</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>16.9</v>
+        <v>4.8</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>120.2</v>
+        <v>638.1</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>136</v>
+        <v>594</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1059,33 +1064,33 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>枫香树社区</t>
+          <t>万达社区</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>39.3</v>
+        <v>72.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3.6</v>
+        <v>10.1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>410.7</v>
+        <v>653.6</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>126</v>
+        <v>501</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>诉求声量高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -1096,33 +1101,33 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>新隆康路社区</t>
+          <t>港务社区</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>36.2</v>
+        <v>1.9</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6.9</v>
+        <v>78.3</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>42.3</v>
+        <v>315.1</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>64</v>
+        <v>417</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>问题指标高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -1133,33 +1138,33 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>西峡社区</t>
+          <t>建设社区</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>105.1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5.1</v>
+        <v>78.8</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>39.7</v>
+        <v>484.8</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>35</v>
+        <v>372</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>问题指标高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -1170,33 +1175,33 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>果园路社区</t>
+          <t>岳湾路社区</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11.8</v>
+        <v>22.9</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>28</v>
+        <v>2.4</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>66.7</v>
+        <v>248.2</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>73</v>
+        <v>225</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>问题指标高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
@@ -1207,33 +1212,33 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>深圳路社区</t>
+          <t>大学路社区</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>61.4</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>45.4</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>22.8</v>
+        <v>6.2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5.5</v>
+        <v>183.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>222</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>问题指标高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -1244,36 +1249,50 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>金安岭社区</t>
+          <t>伍临路社区</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16.1</v>
+        <v>38.2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>19.6</v>
+        <v>14.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>19.6</v>
+        <v>363.6</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>问题指标高</t>
+          <t>主观诉求高·体检未印证</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>排序：双高 → 客观隐患高（按体检点降序）→ 主观诉求高（按诉求件数降序）；密度仅作资格与旁证，不作排序键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>脚注：体检高 = 客观隐患优先整治；诉求高 = 主观诉求集中须回应。两者都是行动对象、同属高优先，只是处置逻辑不同：一处隐患、一应诉求。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
